--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2426-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2426-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE0470F0-810C-478C-9877-A014F55F5AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22E12A9D-D3E8-46FA-B2C5-4BB3EE228485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{F67749A5-60B8-475D-B1F4-BF7F17E045DB}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{00CD9324-F0CD-49FF-9DFF-B371F9702415}"/>
   </bookViews>
   <sheets>
     <sheet name="2426-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1520,26 +1520,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDC4538C-EF6C-4209-BE82-B8E4B59E51AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{651425C3-338F-49A9-BF0E-4B7EFD81EA48}">
   <dimension ref="A1:X45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1573,7 +1573,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1609,7 +1609,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1729,7 +1729,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2024</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>2023</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="36">
         <v>2022</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>2021</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>32</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>32</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>32</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2020</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>32</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>32</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2019</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>32</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>32</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2018</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2017</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2016</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>7.47</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2015</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>9.48</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2014</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2013</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2012</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2011</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>8.1300000000000008</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2010</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2009</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2008</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2007</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>2006</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2005</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>7.63</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>2004</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>2003</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>2002</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>2001</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>2000</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>1999</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>1998</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38">
         <v>1997</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>1996</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="38">
         <v>1995</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="36">
         <v>1994</v>
       </c>
@@ -4479,7 +4479,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="38">
         <v>1993</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="36">
         <v>1992</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="38" t="s">
         <v>60</v>
       </c>
